--- a/Documentation/Documents/SQL Generator/Data Initial/Master.TblPerson.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/Master.TblPerson.xlsx
@@ -4879,21 +4879,7 @@
     <cellStyle name="Normal 2" xfId="1"/>
     <cellStyle name="Normal 2 3" xfId="2"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <fill>
         <patternFill>
@@ -15897,7 +15883,7 @@
     <sortCondition ref="K595:K613"/>
   </sortState>
   <conditionalFormatting sqref="H4:H620">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="0" priority="2">
       <formula>EXACT(H3, H4)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Documentation/Documents/SQL Generator/Data Initial/Master.TblPerson.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/Master.TblPerson.xlsx
@@ -12,13 +12,14 @@
     <sheet name="DataLookUp" sheetId="9" r:id="rId3"/>
     <sheet name="Pindahan dari DB ERP Live" sheetId="2" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="10" r:id="rId6"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2963" uniqueCount="1491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2972" uniqueCount="1500">
   <si>
     <t>Abd Samad</t>
   </si>
@@ -4491,6 +4492,33 @@
   </si>
   <si>
     <t>Photo Log_FileUpload_Pointer_RefID</t>
+  </si>
+  <si>
+    <t>heru.indra</t>
+  </si>
+  <si>
+    <t>budi.santosa</t>
+  </si>
+  <si>
+    <t>haryono</t>
+  </si>
+  <si>
+    <t>indah.sri</t>
+  </si>
+  <si>
+    <t>Heru Indra Permana</t>
+  </si>
+  <si>
+    <t>Indah Sri Rejeki</t>
+  </si>
+  <si>
+    <t>Haryono</t>
+  </si>
+  <si>
+    <t>3172042401092573</t>
+  </si>
+  <si>
+    <t>Budi Santosa (KSO)</t>
   </si>
 </sst>
 </file>
@@ -5244,7 +5272,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="A1:K621"/>
+  <dimension ref="A1:K625"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -5342,7 +5370,7 @@
         <v>25000000000002</v>
       </c>
       <c r="J5" s="20" t="str">
-        <f t="shared" ref="J4:J67" si="1">IF(EXACT(B5, ""), "", CONCATENATE("PERFORM ""SchData-OLTP-Master"".""Func_TblPerson_SET""(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, '", B5, "'::varchar, null::bigint);"))</f>
+        <f t="shared" ref="J5:J67" si="1">IF(EXACT(B5, ""), "", CONCATENATE("PERFORM ""SchData-OLTP-Master"".""Func_TblPerson_SET""(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, '", B5, "'::varchar, null::bigint);"))</f>
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Abdul Karim'::varchar, null::bigint);</v>
       </c>
       <c r="K5" s="1" t="str">
@@ -18242,7 +18270,7 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Taufik Iskandar'::varchar, null::bigint);</v>
       </c>
       <c r="K581" s="1" t="str">
-        <f t="shared" ref="K581:K606" si="29">CONCATENATE(
+        <f t="shared" ref="K581:K624" si="29">CONCATENATE(
 "varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
 "'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
 "'sysLoginSession_RefID', varSystemLoginSession::bigint,",
@@ -18845,23 +18873,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Muhammad Rizal'::varchar, null::bigint);</v>
       </c>
       <c r="K607" s="1" t="str">
-        <f>CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'name', ", IF(EXACT($B2, ""), "null", CONCATENATE("'", SUBSTITUTE($B2, "'", "\'"), "'")), "::varchar,",
-"'acronym', ", IF(EXACT($C2, ""), "null", CONCATENATE("'", SUBSTITUTE($C2, "'", "\'"), "'")), "::varchar,",
-"'SWIFTCode', ", IF(EXACT($E2, ""), "null", CONCATENATE("'", SUBSTITUTE($E2, "'", "\'"), "'")), "::varchar,",
-"'bankCode', ", IF(EXACT($F2, ""), "null", CONCATENATE("'", SUBSTITUTE($F2, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Person Name'::varchar,'acronym', null::varchar,'SWIFTCode', 'Nomor Induk Kependudukan'::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Muhammad Rizal'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="608" spans="1:11" x14ac:dyDescent="0.25">
@@ -18884,23 +18897,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Rahmad Dwifar'::varchar, null::bigint);</v>
       </c>
       <c r="K608" s="1" t="str">
-        <f t="shared" ref="K608:K620" si="30">CONCATENATE(
-"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
-"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
-"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
-"'sysDataAnnotation', NULL::varchar,",
-"'sysDataSetDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
-"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
-"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
-"'sysBranch_RefID', varInstitutionBranchID::bigint,",
-"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
-"'name', ", IF(EXACT($B3, ""), "null", CONCATENATE("'", SUBSTITUTE($B3, "'", "\'"), "'")), "::varchar,",
-"'acronym', ", IF(EXACT($C3, ""), "null", CONCATENATE("'", SUBSTITUTE($C3, "'", "\'"), "'")), "::varchar,",
-"'SWIFTCode', ", IF(EXACT($E3, ""), "null", CONCATENATE("'", SUBSTITUTE($E3, "'", "\'"), "'")), "::varchar,",
-"'bankCode', ", IF(EXACT($F3, ""), "null", CONCATENATE("'", SUBSTITUTE($F3, "'", "\'"), "'")), "::varchar",
-")))::varchar;")</f>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', null::varchar,'acronym', null::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Rahmad Dwifar'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="609" spans="2:11" x14ac:dyDescent="0.25">
@@ -18921,8 +18919,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Reza Sanjaya'::varchar, null::bigint);</v>
       </c>
       <c r="K609" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Abdollah Syani Siregar'::varchar,'acronym', 'Abdollah'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Reza Sanjaya'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="610" spans="2:11" x14ac:dyDescent="0.25">
@@ -18945,8 +18943,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Ridwan Nur Muttaqin'::varchar, null::bigint);</v>
       </c>
       <c r="K610" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Abdul Karim'::varchar,'acronym', 'karim'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Ridwan Nur Muttaqin'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="611" spans="2:11" x14ac:dyDescent="0.25">
@@ -18967,8 +18965,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Risaldi '::varchar, null::bigint);</v>
       </c>
       <c r="K611" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Abdul Rahman Sitompul'::varchar,'acronym', 'abdul'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Risaldi '::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="612" spans="2:11" x14ac:dyDescent="0.25">
@@ -18991,8 +18989,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Risty Alawiyah'::varchar, null::bigint);</v>
       </c>
       <c r="K612" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Abdul Risan'::varchar,'acronym', 'abdul.risan'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Risty Alawiyah'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="613" spans="2:11" x14ac:dyDescent="0.25">
@@ -19013,8 +19011,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Rustono'::varchar, null::bigint);</v>
       </c>
       <c r="K613" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Abdullah Nabil'::varchar,'acronym', 'nabil'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Rustono'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="614" spans="2:11" x14ac:dyDescent="0.25">
@@ -19035,8 +19033,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Solihin'::varchar, null::bigint);</v>
       </c>
       <c r="K614" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Adhitya Danar'::varchar,'acronym', 'adhitya'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Solihin'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="615" spans="2:11" x14ac:dyDescent="0.25">
@@ -19057,8 +19055,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Supriatna'::varchar, null::bigint);</v>
       </c>
       <c r="K615" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Adi Ruswandi'::varchar,'acronym', 'adi'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Supriatna'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="616" spans="2:11" x14ac:dyDescent="0.25">
@@ -19079,8 +19077,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Taufik Aminudin'::varchar, null::bigint);</v>
       </c>
       <c r="K616" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Adietya Dharmawan'::varchar,'acronym', 'adietya.dharmawan'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Taufik Aminudin'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="617" spans="2:11" x14ac:dyDescent="0.25">
@@ -19101,8 +19099,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Timotius Tabun'::varchar, null::bigint);</v>
       </c>
       <c r="K617" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Aditya Yudha Prawira'::varchar,'acronym', 'aditya'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Timotius Tabun'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="618" spans="2:11" x14ac:dyDescent="0.25">
@@ -19123,8 +19121,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Adi'::varchar, null::bigint);</v>
       </c>
       <c r="K618" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Adli Margie'::varchar,'acronym', 'adli'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Adi'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="619" spans="2:11" x14ac:dyDescent="0.25">
@@ -19145,8 +19143,8 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Andrean Fahrizi'::varchar, null::bigint);</v>
       </c>
       <c r="K619" s="1" t="str">
-        <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Afrida Eka Putri'::varchar,'acronym', 'afrida'::varchar,'SWIFTCode', null::varchar,'bankCode', null::varchar)))::varchar;</v>
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Andrean Fahrizi'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
       </c>
     </row>
     <row r="620" spans="2:11" x14ac:dyDescent="0.25">
@@ -19167,26 +19165,113 @@
         <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Amar Abdilah'::varchar, null::bigint);</v>
       </c>
       <c r="K620" s="1" t="str">
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Amar Abdilah'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="621" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B621" s="10" t="s">
+        <v>1495</v>
+      </c>
+      <c r="C621" s="10" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D621" s="10"/>
+      <c r="E621" s="17"/>
+      <c r="I621" s="19">
+        <f t="shared" ref="I621:I624" si="30" xml:space="preserve"> I620 + IF(EXACT(J621, ""), 0, 1)</f>
+        <v>25000000000618</v>
+      </c>
+      <c r="J621" s="20" t="str">
+        <f t="shared" ref="J621:J624" si="31">IF(EXACT(B621, ""), "", CONCATENATE("PERFORM ""SchData-OLTP-Master"".""Func_TblPerson_SET""(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, '", B621, "'::varchar, null::bigint);"))</f>
+        <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Heru Indra Permana'::varchar, null::bigint);</v>
+      </c>
+      <c r="K621" s="1" t="str">
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Heru Indra Permana'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="622" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B622" s="10" t="s">
+        <v>1499</v>
+      </c>
+      <c r="C622" s="10" t="s">
+        <v>1492</v>
+      </c>
+      <c r="D622" s="10"/>
+      <c r="E622" s="17"/>
+      <c r="I622" s="19">
         <f t="shared" si="30"/>
-        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Agnes Sutedja'::varchar,'acronym', 'agnes'::varchar,'SWIFTCode', '3173054608700001'::varchar,'bankCode', null::varchar)))::varchar;</v>
-      </c>
-    </row>
-    <row r="621" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B621" s="11" t="str">
-        <f>IF(EXACT(MAIN!$I621, ""), "", MAIN!$I621)</f>
-        <v/>
-      </c>
-      <c r="C621" s="11"/>
-      <c r="D621" s="11"/>
-      <c r="E621" s="18"/>
-      <c r="I621" s="21"/>
-      <c r="J621" s="11"/>
+        <v>25000000000619</v>
+      </c>
+      <c r="J622" s="20" t="str">
+        <f t="shared" si="31"/>
+        <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Budi Santosa (KSO)'::varchar, null::bigint);</v>
+      </c>
+      <c r="K622" s="1" t="str">
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Budi Santosa (KSO)'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="623" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B623" s="10" t="s">
+        <v>1497</v>
+      </c>
+      <c r="C623" s="10" t="s">
+        <v>1493</v>
+      </c>
+      <c r="D623" s="10"/>
+      <c r="E623" s="17"/>
+      <c r="I623" s="19">
+        <f t="shared" si="30"/>
+        <v>25000000000620</v>
+      </c>
+      <c r="J623" s="20" t="str">
+        <f t="shared" si="31"/>
+        <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Haryono'::varchar, null::bigint);</v>
+      </c>
+      <c r="K623" s="1" t="str">
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Haryono'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="624" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B624" s="10" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C624" s="10" t="s">
+        <v>1494</v>
+      </c>
+      <c r="D624" s="10"/>
+      <c r="E624" s="17" t="s">
+        <v>1498</v>
+      </c>
+      <c r="I624" s="19">
+        <f t="shared" si="30"/>
+        <v>25000000000621</v>
+      </c>
+      <c r="J624" s="20" t="str">
+        <f t="shared" si="31"/>
+        <v>PERFORM "SchData-OLTP-Master"."Func_TblPerson_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Indah Sri Rejeki'::varchar, null::bigint);</v>
+      </c>
+      <c r="K624" s="1" t="str">
+        <f t="shared" si="29"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Indah Sri Rejeki'::varchar,'photo_Log_FileUpload_Pointer_RefID', null::bigint)))::varchar;</v>
+      </c>
+    </row>
+    <row r="625" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B625" s="11"/>
+      <c r="C625" s="11"/>
+      <c r="D625" s="11"/>
+      <c r="E625" s="18"/>
+      <c r="I625" s="21"/>
+      <c r="J625" s="11"/>
     </row>
   </sheetData>
   <sortState ref="L595:L613">
     <sortCondition ref="L595:L613"/>
   </sortState>
-  <conditionalFormatting sqref="I4:I620">
+  <conditionalFormatting sqref="I4:I624">
     <cfRule type="expression" dxfId="0" priority="2">
       <formula>EXACT(I3, I4)</formula>
     </cfRule>
@@ -19194,7 +19279,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="E442 E595:E596 E608 E15 E516 E78 E85 E95 E109 E119 E126 E129 E128 E141 E171 E199 E530 E531 E235 E256 E265 E158 E279 E604 E607 E304 E310 E577 E539 E610 E612 E355 E394 E396 E400 E415 E281 E582 E455 E545 E584 E548 E490 E500 E504 E350 E170 E562 E20 E512 E54 E598:E599 E520 E96 E553 E123 E524 E591 E554 E375 E613:E615 E418 E551 E461 E617:E618" numberStoredAsText="1"/>
+    <ignoredError sqref="E442 E595:E596 E608 E15 E516 E78 E85 E95 E109 E119 E126 E129 E128 E141 E171 E199 E530 E531 E235 E256 E265 E158 E279 E604 E607 E304 E310 E577 E539 E610 E612 E355 E394 E396 E400 E415 E281 E582 E455 E545 E584 E548 E490 E500 E504 E350 E170 E562 E20 E512 E54 E598:E599 E520 E96 E553 E123 E524 E591 E554 E375 E613:E615 E418 E551 E461 E617:E618 E624" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -19204,7 +19289,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B1:D646"/>
+  <dimension ref="B1:D650"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -27870,65 +27955,109 @@
       </c>
     </row>
     <row r="621" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B621" s="26"/>
-      <c r="C621" s="29"/>
-      <c r="D621" s="29"/>
+      <c r="B621" s="25">
+        <f>IF(EXACT(MAIN!$I621, ""), "", MAIN!$I621)</f>
+        <v>25000000000618</v>
+      </c>
+      <c r="C621" s="28" t="str">
+        <f>IF(EXACT(MAIN!$B621, ""), "", MAIN!$B621)</f>
+        <v>Heru Indra Permana</v>
+      </c>
+      <c r="D621" s="28" t="str">
+        <f>IF(EXACT($B621, ""), "", IF(EXACT(MAIN!$E621, ""), "", MAIN!$E621))</f>
+        <v/>
+      </c>
     </row>
     <row r="622" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B622" s="2"/>
+      <c r="B622" s="25">
+        <f>IF(EXACT(MAIN!$I622, ""), "", MAIN!$I622)</f>
+        <v>25000000000619</v>
+      </c>
+      <c r="C622" s="28" t="str">
+        <f>IF(EXACT(MAIN!$B622, ""), "", MAIN!$B622)</f>
+        <v>Budi Santosa (KSO)</v>
+      </c>
+      <c r="D622" s="28" t="str">
+        <f>IF(EXACT($B622, ""), "", IF(EXACT(MAIN!$E622, ""), "", MAIN!$E622))</f>
+        <v/>
+      </c>
     </row>
     <row r="623" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B623" s="2"/>
+      <c r="B623" s="25">
+        <f>IF(EXACT(MAIN!$I623, ""), "", MAIN!$I623)</f>
+        <v>25000000000620</v>
+      </c>
+      <c r="C623" s="28" t="str">
+        <f>IF(EXACT(MAIN!$B623, ""), "", MAIN!$B623)</f>
+        <v>Haryono</v>
+      </c>
+      <c r="D623" s="28" t="str">
+        <f>IF(EXACT($B623, ""), "", IF(EXACT(MAIN!$E623, ""), "", MAIN!$E623))</f>
+        <v/>
+      </c>
     </row>
     <row r="624" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B624" s="2"/>
-    </row>
-    <row r="625" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B625" s="2"/>
-    </row>
-    <row r="626" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B624" s="25">
+        <f>IF(EXACT(MAIN!$I624, ""), "", MAIN!$I624)</f>
+        <v>25000000000621</v>
+      </c>
+      <c r="C624" s="28" t="str">
+        <f>IF(EXACT(MAIN!$B624, ""), "", MAIN!$B624)</f>
+        <v>Indah Sri Rejeki</v>
+      </c>
+      <c r="D624" s="28" t="str">
+        <f>IF(EXACT($B624, ""), "", IF(EXACT(MAIN!$E624, ""), "", MAIN!$E624))</f>
+        <v>3172042401092573</v>
+      </c>
+    </row>
+    <row r="625" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B625" s="26"/>
+      <c r="C625" s="29"/>
+      <c r="D625" s="29"/>
+    </row>
+    <row r="626" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B626" s="2"/>
     </row>
-    <row r="627" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="627" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B627" s="2"/>
     </row>
-    <row r="628" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="628" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B628" s="2"/>
     </row>
-    <row r="629" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="629" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B629" s="2"/>
     </row>
-    <row r="630" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="630" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B630" s="2"/>
     </row>
-    <row r="631" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="631" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B631" s="2"/>
     </row>
-    <row r="632" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="632" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B632" s="2"/>
     </row>
-    <row r="633" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="633" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B633" s="2"/>
     </row>
-    <row r="634" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="634" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B634" s="2"/>
     </row>
-    <row r="635" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="635" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B635" s="2"/>
     </row>
-    <row r="636" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="636" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B636" s="2"/>
     </row>
-    <row r="637" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="637" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B637" s="2"/>
     </row>
-    <row r="638" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="638" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B638" s="2"/>
     </row>
-    <row r="639" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="639" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B639" s="2"/>
     </row>
-    <row r="640" spans="2:2" x14ac:dyDescent="0.2">
+    <row r="640" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B640" s="2"/>
     </row>
     <row r="641" spans="2:2" x14ac:dyDescent="0.2">
@@ -27948,6 +28077,18 @@
     </row>
     <row r="646" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B646" s="2"/>
+    </row>
+    <row r="647" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B647" s="2"/>
+    </row>
+    <row r="648" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B648" s="2"/>
+    </row>
+    <row r="649" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B649" s="2"/>
+    </row>
+    <row r="650" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B650" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -35108,4 +35249,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>